--- a/data/hex_xlsx/UPM.HE.xlsx
+++ b/data/hex_xlsx/UPM.HE.xlsx
@@ -15853,14 +15853,38 @@
       <c r="P74" s="15">
         <v>50327.23</v>
       </c>
-      <c r="Q74" s="15"/>
-      <c r="R74" s="15"/>
-      <c r="S74" s="15"/>
-      <c r="T74" s="15"/>
-      <c r="U74" s="15"/>
-      <c r="V74" s="15"/>
-      <c r="W74" s="15"/>
-      <c r="X74" s="15"/>
+      <c r="Q74" s="15">
+        <f t="shared" ref="Q74:X74" si="1">Q75+Q79+Q83+Q87</f>
+        <v>45636.75</v>
+      </c>
+      <c r="R74" s="15">
+        <f t="shared" si="1"/>
+        <v>51015.29</v>
+      </c>
+      <c r="S74" s="15">
+        <f t="shared" si="1"/>
+        <v>53938.41</v>
+      </c>
+      <c r="T74" s="15">
+        <f t="shared" si="1"/>
+        <v>46121.02</v>
+      </c>
+      <c r="U74" s="15">
+        <f t="shared" si="1"/>
+        <v>51231.98</v>
+      </c>
+      <c r="V74" s="15">
+        <f t="shared" si="1"/>
+        <v>55794.61</v>
+      </c>
+      <c r="W74" s="15">
+        <f t="shared" si="1"/>
+        <v>60680.09</v>
+      </c>
+      <c r="X74" s="15">
+        <f t="shared" si="1"/>
+        <v>65120.81</v>
+      </c>
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
@@ -18838,7 +18862,9 @@
       <c r="O129" s="16">
         <v>1974.41</v>
       </c>
-      <c r="P129" s="15"/>
+      <c r="P129" s="16">
+        <v>7009.45</v>
+      </c>
       <c r="Q129" s="16">
         <v>2227.32</v>
       </c>

--- a/data/hex_xlsx/UPM.HE.xlsx
+++ b/data/hex_xlsx/UPM.HE.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="562">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -819,258 +819,261 @@
     <t>Other current financial assets</t>
   </si>
   <si>
+    <t>Derivative Financial Instruments ASSET</t>
+  </si>
+  <si>
+    <t>Investment funds</t>
+  </si>
+  <si>
+    <t>Loans/Notes Receivables - Net</t>
+  </si>
+  <si>
+    <t>Available-for-Sale Investments</t>
+  </si>
+  <si>
+    <t>Balancing Item - Current Assets</t>
+  </si>
+  <si>
+    <t>Current Assets</t>
+  </si>
+  <si>
+    <t>Goodwill</t>
+  </si>
+  <si>
+    <t>Other intangible assets</t>
+  </si>
+  <si>
+    <t>Emission rights, net carrying value</t>
+  </si>
+  <si>
+    <t>License , gross</t>
+  </si>
+  <si>
+    <t>Acc Amortization/Imp Emission Rights</t>
+  </si>
+  <si>
+    <t>Construction in Progress, Net</t>
+  </si>
+  <si>
+    <t>Construction in Progress, Gross</t>
+  </si>
+  <si>
+    <t>Intangible Rights , Net</t>
+  </si>
+  <si>
+    <t>Intangible Rights Gross</t>
+  </si>
+  <si>
+    <t>Accumulated amortisation and impairment Intangible Rights</t>
+  </si>
+  <si>
+    <t>Intangible Rights , Net - Balancing value</t>
+  </si>
+  <si>
+    <t>Other Intangibles, Net</t>
+  </si>
+  <si>
+    <t>Other Intangibles, Gross</t>
+  </si>
+  <si>
+    <t>Acc Amortization /Imp Other Intangibles</t>
+  </si>
+  <si>
+    <t>Software &amp; other Intangible Assets - Gross</t>
+  </si>
+  <si>
+    <t>Computer Software - Intangible Assets - Accumulated Amortization &amp; Impairment</t>
+  </si>
+  <si>
+    <t>Software &amp; other Intangible Assets - Net - Balancing value</t>
+  </si>
+  <si>
+    <t>Other intangible assets - Balancing value</t>
+  </si>
+  <si>
+    <t>Forest assets</t>
+  </si>
+  <si>
+    <t>Investment property</t>
+  </si>
+  <si>
+    <t>Acc Depreciation Investment Property</t>
+  </si>
+  <si>
+    <t>Investment Property gross</t>
+  </si>
+  <si>
+    <t>Property, plant and equipment</t>
+  </si>
+  <si>
+    <t>Land/Water Areas, Net</t>
+  </si>
+  <si>
+    <t>Land/Water Areas Gross</t>
+  </si>
+  <si>
+    <t>Accumulated depreciation and impairments/Imp Land/Water Areas</t>
+  </si>
+  <si>
+    <t>Land/Water Areas, Net - Balancing value</t>
+  </si>
+  <si>
+    <t>Buildings-net</t>
+  </si>
+  <si>
+    <t>Buildings</t>
+  </si>
+  <si>
+    <t>Accumulated depreciation and impairments Buildings</t>
+  </si>
+  <si>
+    <t>Buildings-net - Balancing value</t>
+  </si>
+  <si>
+    <t>Plant/Machinery/Equipment, Net</t>
+  </si>
+  <si>
+    <t>Machinery/Equip.</t>
+  </si>
+  <si>
+    <t>Accumulated depreciation and impairments Plant/Machinery/Equipment</t>
+  </si>
+  <si>
+    <t>Plant/Machinery/Equipment, Net - Balancing value</t>
+  </si>
+  <si>
+    <t>Other Tangible Fixed Assets, Net</t>
+  </si>
+  <si>
+    <t>Other Tangibles</t>
+  </si>
+  <si>
+    <t>Accumulated depreciation and impairments Other Tangible Fixed Assets</t>
+  </si>
+  <si>
+    <t>Other Tangible Fixed Assets, Net - Balancing value</t>
+  </si>
+  <si>
+    <t>Construction in Progress - Accumulated Depreciation &amp; Impairment</t>
+  </si>
+  <si>
+    <t>Construction in Progress, Net - Balancing value</t>
+  </si>
+  <si>
+    <t>Property, plant and equipment - Balancing value</t>
+  </si>
+  <si>
+    <t>Investments in associates and joint ventures</t>
+  </si>
+  <si>
+    <t>Energy shareholdings</t>
+  </si>
+  <si>
+    <t>Other non-current financial assets</t>
+  </si>
+  <si>
+    <t>Non Current Derivative Financial Instrument-hedging</t>
+  </si>
+  <si>
+    <t>Receivables</t>
+  </si>
+  <si>
+    <t>Other non-current financial assets - Balancing value</t>
+  </si>
+  <si>
+    <t>Tax Recoverable</t>
+  </si>
+  <si>
+    <t>Deferred tax assets</t>
+  </si>
+  <si>
+    <t>Other non-current assets</t>
+  </si>
+  <si>
+    <t>Net retirement benefit assets</t>
+  </si>
+  <si>
+    <t>Balancing Item - Noncurrent Assets</t>
+  </si>
+  <si>
+    <t>Leased assets</t>
+  </si>
+  <si>
+    <t>Non-current assets</t>
+  </si>
+  <si>
+    <t>Assets classified as held for sale</t>
+  </si>
+  <si>
+    <t>Balancing Item - Assets</t>
+  </si>
+  <si>
+    <t>Assets</t>
+  </si>
+  <si>
+    <t>Trade and other payables</t>
+  </si>
+  <si>
+    <t>Advances Received</t>
+  </si>
+  <si>
+    <t>Amounts due to associates and joint ventures</t>
+  </si>
+  <si>
+    <t>Accrued expenses and deferred income</t>
+  </si>
+  <si>
+    <t>Personnel expenses</t>
+  </si>
+  <si>
+    <t>Interest expenses</t>
+  </si>
+  <si>
+    <t>Accrued expenses and deferred income - Balancing value</t>
+  </si>
+  <si>
+    <t>Advances received</t>
+  </si>
+  <si>
+    <t>Trade payables</t>
+  </si>
+  <si>
+    <t>Other Current Liabilities</t>
+  </si>
+  <si>
+    <t>Trade and other payables - Balancing value</t>
+  </si>
+  <si>
+    <t>Income tax payables</t>
+  </si>
+  <si>
+    <t>Other current financial liabilities</t>
+  </si>
+  <si>
+    <t>Liabilities related to assets classified as held for sale</t>
+  </si>
+  <si>
+    <t>Current debt</t>
+  </si>
+  <si>
+    <t>Current Portion of Long-Term Debt excluding Capitalized Leases</t>
+  </si>
+  <si>
+    <t>Repayments of non-current debt</t>
+  </si>
+  <si>
+    <t>Current portion of debt - Balancing value</t>
+  </si>
+  <si>
+    <t>Repayments of lease liabilities</t>
+  </si>
+  <si>
+    <t>Current loans</t>
+  </si>
+  <si>
     <t>Derivative Financial Instruments</t>
   </si>
   <si>
-    <t>Investment funds</t>
-  </si>
-  <si>
-    <t>Loans/Notes Receivables - Net</t>
-  </si>
-  <si>
-    <t>Available-for-Sale Investments</t>
-  </si>
-  <si>
-    <t>Balancing Item - Current Assets</t>
-  </si>
-  <si>
-    <t>Current Assets</t>
-  </si>
-  <si>
-    <t>Goodwill</t>
-  </si>
-  <si>
-    <t>Other intangible assets</t>
-  </si>
-  <si>
-    <t>Emission rights, net carrying value</t>
-  </si>
-  <si>
-    <t>License , gross</t>
-  </si>
-  <si>
-    <t>Acc Amortization/Imp Emission Rights</t>
-  </si>
-  <si>
-    <t>Construction in Progress, Net</t>
-  </si>
-  <si>
-    <t>Construction in Progress, Gross</t>
-  </si>
-  <si>
-    <t>Intangible Rights , Net</t>
-  </si>
-  <si>
-    <t>Intangible Rights Gross</t>
-  </si>
-  <si>
-    <t>Accumulated amortisation and impairment Intangible Rights</t>
-  </si>
-  <si>
-    <t>Intangible Rights , Net - Balancing value</t>
-  </si>
-  <si>
-    <t>Other Intangibles, Net</t>
-  </si>
-  <si>
-    <t>Other Intangibles, Gross</t>
-  </si>
-  <si>
-    <t>Acc Amortization /Imp Other Intangibles</t>
-  </si>
-  <si>
-    <t>Software &amp; other Intangible Assets - Gross</t>
-  </si>
-  <si>
-    <t>Computer Software - Intangible Assets - Accumulated Amortization &amp; Impairment</t>
-  </si>
-  <si>
-    <t>Software &amp; other Intangible Assets - Net - Balancing value</t>
-  </si>
-  <si>
-    <t>Other intangible assets - Balancing value</t>
-  </si>
-  <si>
-    <t>Forest assets</t>
-  </si>
-  <si>
-    <t>Investment property</t>
-  </si>
-  <si>
-    <t>Acc Depreciation Investment Property</t>
-  </si>
-  <si>
-    <t>Investment Property gross</t>
-  </si>
-  <si>
-    <t>Property, plant and equipment</t>
-  </si>
-  <si>
-    <t>Land/Water Areas, Net</t>
-  </si>
-  <si>
-    <t>Land/Water Areas Gross</t>
-  </si>
-  <si>
-    <t>Accumulated depreciation and impairments/Imp Land/Water Areas</t>
-  </si>
-  <si>
-    <t>Land/Water Areas, Net - Balancing value</t>
-  </si>
-  <si>
-    <t>Buildings-net</t>
-  </si>
-  <si>
-    <t>Buildings</t>
-  </si>
-  <si>
-    <t>Accumulated depreciation and impairments Buildings</t>
-  </si>
-  <si>
-    <t>Buildings-net - Balancing value</t>
-  </si>
-  <si>
-    <t>Plant/Machinery/Equipment, Net</t>
-  </si>
-  <si>
-    <t>Machinery/Equip.</t>
-  </si>
-  <si>
-    <t>Accumulated depreciation and impairments Plant/Machinery/Equipment</t>
-  </si>
-  <si>
-    <t>Plant/Machinery/Equipment, Net - Balancing value</t>
-  </si>
-  <si>
-    <t>Other Tangible Fixed Assets, Net</t>
-  </si>
-  <si>
-    <t>Other Tangibles</t>
-  </si>
-  <si>
-    <t>Accumulated depreciation and impairments Other Tangible Fixed Assets</t>
-  </si>
-  <si>
-    <t>Other Tangible Fixed Assets, Net - Balancing value</t>
-  </si>
-  <si>
-    <t>Construction in Progress - Accumulated Depreciation &amp; Impairment</t>
-  </si>
-  <si>
-    <t>Construction in Progress, Net - Balancing value</t>
-  </si>
-  <si>
-    <t>Property, plant and equipment - Balancing value</t>
-  </si>
-  <si>
-    <t>Investments in associates and joint ventures</t>
-  </si>
-  <si>
-    <t>Energy shareholdings</t>
-  </si>
-  <si>
-    <t>Other non-current financial assets</t>
-  </si>
-  <si>
-    <t>Non Current Derivative Financial Instrument-hedging</t>
-  </si>
-  <si>
-    <t>Receivables</t>
-  </si>
-  <si>
-    <t>Other non-current financial assets - Balancing value</t>
-  </si>
-  <si>
-    <t>Tax Recoverable</t>
-  </si>
-  <si>
-    <t>Deferred tax assets</t>
-  </si>
-  <si>
-    <t>Other non-current assets</t>
-  </si>
-  <si>
-    <t>Net retirement benefit assets</t>
-  </si>
-  <si>
-    <t>Balancing Item - Noncurrent Assets</t>
-  </si>
-  <si>
-    <t>Leased assets</t>
-  </si>
-  <si>
-    <t>Non-current assets</t>
-  </si>
-  <si>
-    <t>Assets classified as held for sale</t>
-  </si>
-  <si>
-    <t>Balancing Item - Assets</t>
-  </si>
-  <si>
-    <t>Assets</t>
-  </si>
-  <si>
-    <t>Trade and other payables</t>
-  </si>
-  <si>
-    <t>Advances Received</t>
-  </si>
-  <si>
-    <t>Amounts due to associates and joint ventures</t>
-  </si>
-  <si>
-    <t>Accrued expenses and deferred income</t>
-  </si>
-  <si>
-    <t>Personnel expenses</t>
-  </si>
-  <si>
-    <t>Interest expenses</t>
-  </si>
-  <si>
-    <t>Accrued expenses and deferred income - Balancing value</t>
-  </si>
-  <si>
-    <t>Advances received</t>
-  </si>
-  <si>
-    <t>Trade payables</t>
-  </si>
-  <si>
-    <t>Other Current Liabilities</t>
-  </si>
-  <si>
-    <t>Trade and other payables - Balancing value</t>
-  </si>
-  <si>
-    <t>Income tax payables</t>
-  </si>
-  <si>
-    <t>Other current financial liabilities</t>
-  </si>
-  <si>
-    <t>Liabilities related to assets classified as held for sale</t>
-  </si>
-  <si>
-    <t>Current debt</t>
-  </si>
-  <si>
-    <t>Current Portion of Long-Term Debt excluding Capitalized Leases</t>
-  </si>
-  <si>
-    <t>Repayments of non-current debt</t>
-  </si>
-  <si>
-    <t>Current portion of debt - Balancing value</t>
-  </si>
-  <si>
-    <t>Repayments of lease liabilities</t>
-  </si>
-  <si>
-    <t>Current loans</t>
-  </si>
-  <si>
     <t>Other Liabilities</t>
   </si>
   <si>
@@ -1098,7 +1101,7 @@
     <t>Other Liabilities - Non-current</t>
   </si>
   <si>
-    <t>Derivative financial instrument</t>
+    <t>Derivative financial instrument LT</t>
   </si>
   <si>
     <t>Net retirement benefit liabilities</t>
@@ -1123,6 +1126,9 @@
   </si>
   <si>
     <t>Lease Liabilities</t>
+  </si>
+  <si>
+    <t>Derivative Financial Instruments LT</t>
   </si>
   <si>
     <t>Loans from financials institutions</t>
@@ -14459,7 +14465,7 @@
       <c r="X45" s="15"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="14" t="s">
+      <c r="A46" s="23" t="s">
         <v>266</v>
       </c>
       <c r="B46" s="16">
@@ -19050,7 +19056,7 @@
     </row>
     <row r="133" ht="15.0" customHeight="1">
       <c r="A133" s="14" t="s">
-        <v>266</v>
+        <v>350</v>
       </c>
       <c r="B133" s="21">
         <v>35.44</v>
@@ -19114,7 +19120,7 @@
     </row>
     <row r="134" ht="15.0" customHeight="1">
       <c r="A134" s="14" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B134" s="15"/>
       <c r="C134" s="15"/>
@@ -19148,7 +19154,7 @@
     </row>
     <row r="135" ht="15.0" customHeight="1">
       <c r="A135" s="14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B135" s="20">
         <v>-11.81</v>
@@ -19180,7 +19186,7 @@
     </row>
     <row r="136" ht="15.0" customHeight="1">
       <c r="A136" s="14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B136" s="15"/>
       <c r="C136" s="15"/>
@@ -19220,7 +19226,7 @@
     </row>
     <row r="137" ht="15.0" customHeight="1">
       <c r="A137" s="14" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B137" s="16">
         <v>2114.71</v>
@@ -19252,7 +19258,7 @@
     </row>
     <row r="138" ht="15.0" customHeight="1">
       <c r="A138" s="14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B138" s="15"/>
       <c r="C138" s="15"/>
@@ -19282,7 +19288,7 @@
     </row>
     <row r="139" ht="15.0" customHeight="1">
       <c r="A139" s="14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B139" s="21">
         <v>11.81</v>
@@ -19326,7 +19332,7 @@
     </row>
     <row r="140" ht="15.0" customHeight="1">
       <c r="A140" s="17" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B140" s="18">
         <v>26427.93</v>
@@ -19400,7 +19406,7 @@
     </row>
     <row r="141" ht="15.0" customHeight="1">
       <c r="A141" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B141" s="16">
         <v>8175.29</v>
@@ -19474,7 +19480,7 @@
     </row>
     <row r="142" ht="15.0" customHeight="1">
       <c r="A142" s="14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B142" s="16">
         <v>1063.26</v>
@@ -19548,7 +19554,7 @@
     </row>
     <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="14" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B143" s="16">
         <v>1016.0</v>
@@ -19605,8 +19611,8 @@
       <c r="X143" s="15"/>
     </row>
     <row r="144" ht="15.0" customHeight="1">
-      <c r="A144" s="14" t="s">
-        <v>359</v>
+      <c r="A144" s="23" t="s">
+        <v>360</v>
       </c>
       <c r="B144" s="21">
         <v>47.26</v>
@@ -19664,7 +19670,7 @@
     </row>
     <row r="145" ht="15.0" customHeight="1">
       <c r="A145" s="14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B145" s="16">
         <v>5186.35</v>
@@ -19738,7 +19744,7 @@
     </row>
     <row r="146" ht="15.0" customHeight="1">
       <c r="A146" s="14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B146" s="16">
         <v>1193.21</v>
@@ -19812,7 +19818,7 @@
     </row>
     <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B147" s="16">
         <v>826.98</v>
@@ -19870,7 +19876,7 @@
     </row>
     <row r="148" ht="15.0" customHeight="1">
       <c r="A148" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B148" s="16">
         <v>342.61</v>
@@ -19928,7 +19934,7 @@
     </row>
     <row r="149" ht="15.0" customHeight="1">
       <c r="A149" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B149" s="21">
         <v>23.63</v>
@@ -19988,7 +19994,7 @@
     </row>
     <row r="150" ht="15.0" customHeight="1">
       <c r="A150" s="14" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B150" s="15"/>
       <c r="C150" s="15"/>
@@ -20026,7 +20032,7 @@
     </row>
     <row r="151" ht="15.0" customHeight="1">
       <c r="A151" s="14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B151" s="15">
         <v>42979.36</v>
@@ -20092,7 +20098,7 @@
     </row>
     <row r="152" ht="15.0" customHeight="1">
       <c r="A152" s="14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B152" s="16">
         <v>8057.15</v>
@@ -20151,8 +20157,8 @@
       </c>
     </row>
     <row r="153" ht="15.0" customHeight="1">
-      <c r="A153" s="14" t="s">
-        <v>266</v>
+      <c r="A153" s="23" t="s">
+        <v>369</v>
       </c>
       <c r="B153" s="16">
         <v>1311.35</v>
@@ -20216,7 +20222,7 @@
     </row>
     <row r="154" ht="15.0" customHeight="1">
       <c r="A154" s="14" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B154" s="15">
         <v>33610.85</v>
@@ -20284,7 +20290,7 @@
     </row>
     <row r="155" ht="15.0" customHeight="1">
       <c r="A155" s="14" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B155" s="15"/>
       <c r="C155" s="15"/>
@@ -20332,7 +20338,7 @@
     </row>
     <row r="156" ht="15.0" customHeight="1">
       <c r="A156" s="14" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B156" s="15"/>
       <c r="C156" s="15"/>
@@ -20374,7 +20380,7 @@
     </row>
     <row r="157" ht="15.0" customHeight="1">
       <c r="A157" s="14" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B157" s="15"/>
       <c r="C157" s="15"/>
@@ -20416,7 +20422,7 @@
     </row>
     <row r="158" ht="15.0" customHeight="1">
       <c r="A158" s="14" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B158" s="15"/>
       <c r="C158" s="15"/>
@@ -20452,7 +20458,7 @@
     </row>
     <row r="159" ht="15.0" customHeight="1">
       <c r="A159" s="14" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B159" s="15"/>
       <c r="C159" s="15"/>
@@ -20486,7 +20492,7 @@
     </row>
     <row r="160" ht="15.0" customHeight="1">
       <c r="A160" s="14" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B160" s="15"/>
       <c r="C160" s="15"/>
@@ -20520,7 +20526,7 @@
     </row>
     <row r="161" ht="15.0" customHeight="1">
       <c r="A161" s="14" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B161" s="21">
         <v>11.81</v>
@@ -20554,7 +20560,7 @@
     </row>
     <row r="162" ht="15.0" customHeight="1">
       <c r="A162" s="17" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B162" s="18">
         <v>58609.29</v>
@@ -20662,7 +20668,7 @@
     </row>
     <row r="164" ht="15.0" customHeight="1">
       <c r="A164" s="14" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B164" s="20">
         <v>-11.81</v>
@@ -20698,7 +20704,7 @@
     </row>
     <row r="165" ht="15.0" customHeight="1">
       <c r="A165" s="17" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B165" s="18">
         <v>85025.41</v>
@@ -20772,7 +20778,7 @@
     </row>
     <row r="166" ht="15.0" customHeight="1">
       <c r="A166" s="14" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B166" s="15">
         <v>10514.47</v>
@@ -20846,7 +20852,7 @@
     </row>
     <row r="167" ht="15.0" customHeight="1">
       <c r="A167" s="14" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B167" s="20">
         <v>-23.63</v>
@@ -20908,7 +20914,7 @@
     </row>
     <row r="168" ht="15.0" customHeight="1">
       <c r="A168" s="14" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B168" s="16">
         <v>177.21</v>
@@ -20982,7 +20988,7 @@
     </row>
     <row r="169" ht="15.0" customHeight="1">
       <c r="A169" s="14" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B169" s="15">
         <v>19162.32</v>
@@ -21056,7 +21062,7 @@
     </row>
     <row r="170" ht="15.0" customHeight="1">
       <c r="A170" s="14" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B170" s="15">
         <v>18595.25</v>
@@ -21112,7 +21118,7 @@
     </row>
     <row r="171" ht="15.0" customHeight="1">
       <c r="A171" s="14" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B171" s="16">
         <v>330.79</v>
@@ -21168,7 +21174,7 @@
     </row>
     <row r="172" ht="15.0" customHeight="1">
       <c r="A172" s="14" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B172" s="16">
         <v>224.47</v>
@@ -21224,7 +21230,7 @@
     </row>
     <row r="173" ht="15.0" customHeight="1">
       <c r="A173" s="14" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B173" s="21">
         <v>11.81</v>
@@ -21262,7 +21268,7 @@
     </row>
     <row r="174" ht="15.0" customHeight="1">
       <c r="A174" s="14" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B174" s="15"/>
       <c r="C174" s="15"/>
@@ -21296,7 +21302,7 @@
     </row>
     <row r="175" ht="15.0" customHeight="1">
       <c r="A175" s="14" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B175" s="15"/>
       <c r="C175" s="15"/>
@@ -21340,7 +21346,7 @@
     </row>
     <row r="176" ht="15.0" customHeight="1">
       <c r="A176" s="14" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B176" s="15">
         <v>15039.23</v>
@@ -21406,7 +21412,7 @@
     </row>
     <row r="177" ht="15.0" customHeight="1">
       <c r="A177" s="14" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B177" s="15">
         <v>73305.91</v>
@@ -21480,7 +21486,7 @@
     </row>
     <row r="178" ht="15.0" customHeight="1">
       <c r="A178" s="14" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B178" s="15"/>
       <c r="C178" s="15"/>
@@ -21514,7 +21520,7 @@
     </row>
     <row r="179" ht="15.0" customHeight="1">
       <c r="A179" s="14" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B179" s="20">
         <v>-23.63</v>
@@ -21556,7 +21562,7 @@
     </row>
     <row r="180" ht="15.0" customHeight="1">
       <c r="A180" s="17" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B180" s="18">
         <v>118151.88</v>
@@ -21704,7 +21710,7 @@
     </row>
     <row r="182" ht="15.0" customHeight="1">
       <c r="A182" s="17" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B182" s="24">
         <v>3934.06</v>
@@ -21760,7 +21766,7 @@
     </row>
     <row r="183" ht="15.0" customHeight="1">
       <c r="A183" s="14" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B183" s="21">
         <v>11.81</v>
@@ -21796,7 +21802,7 @@
     </row>
     <row r="184" ht="15.0" customHeight="1">
       <c r="A184" s="17" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B184" s="18">
         <v>122097.76</v>
@@ -21870,7 +21876,7 @@
     </row>
     <row r="185" ht="15.0" customHeight="1">
       <c r="A185" s="14" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B185" s="15"/>
       <c r="C185" s="15"/>
@@ -21904,7 +21910,7 @@
     </row>
     <row r="186" ht="15.0" customHeight="1">
       <c r="A186" s="17" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B186" s="18">
         <v>207123.17</v>
@@ -21978,7 +21984,7 @@
     </row>
     <row r="187" ht="15.0" customHeight="1">
       <c r="A187" s="14" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B187" s="16">
         <v>527.74</v>
@@ -22052,7 +22058,7 @@
     </row>
     <row r="188" ht="15.0" customHeight="1">
       <c r="A188" s="14" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B188" s="16">
         <v>527.32</v>
@@ -22126,7 +22132,7 @@
     </row>
     <row r="189" ht="15.0" customHeight="1">
       <c r="A189" s="14" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B189" s="21">
         <v>0.41</v>
@@ -22200,7 +22206,7 @@
     </row>
     <row r="190" ht="15.0" customHeight="1">
       <c r="A190" s="14" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B190" s="15"/>
       <c r="C190" s="15">
@@ -22266,7 +22272,7 @@
     </row>
     <row r="191" ht="15.0" customHeight="1">
       <c r="A191" s="14" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B191" s="15"/>
       <c r="C191" s="15"/>
@@ -22298,7 +22304,7 @@
     </row>
     <row r="192" ht="15.0" customHeight="1">
       <c r="A192" s="14" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B192" s="16">
         <v>756.1</v>
@@ -22366,7 +22372,7 @@
     </row>
     <row r="193" ht="15.0" customHeight="1">
       <c r="A193" s="14" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B193" s="16">
         <v>4134.9</v>
@@ -22434,7 +22440,7 @@
     </row>
     <row r="194" ht="15.0" customHeight="1">
       <c r="A194" s="14" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B194" s="16">
         <v>9226.74</v>
@@ -22502,7 +22508,7 @@
     </row>
     <row r="195" ht="15.0" customHeight="1">
       <c r="A195" s="14" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B195" s="16">
         <v>7620.03</v>
@@ -22570,7 +22576,7 @@
     </row>
     <row r="196" ht="15.0" customHeight="1">
       <c r="A196" s="14" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B196" s="16">
         <v>366.23</v>
@@ -22638,7 +22644,7 @@
     </row>
     <row r="197" ht="15.0" customHeight="1">
       <c r="A197" s="14" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B197" s="15">
         <v>12995.41</v>
@@ -22706,7 +22712,7 @@
     </row>
     <row r="198" ht="15.0" customHeight="1">
       <c r="A198" s="14" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B198" s="15"/>
       <c r="C198" s="15"/>
@@ -22740,7 +22746,7 @@
     </row>
     <row r="199" ht="15.0" customHeight="1">
       <c r="A199" s="14" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B199" s="15"/>
       <c r="C199" s="16">
@@ -22806,7 +22812,7 @@
     </row>
     <row r="200" ht="15.0" customHeight="1">
       <c r="A200" s="14" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B200" s="15"/>
       <c r="C200" s="15"/>
@@ -22844,7 +22850,7 @@
     </row>
     <row r="201" ht="15.0" customHeight="1">
       <c r="A201" s="14" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B201" s="15"/>
       <c r="C201" s="15"/>
@@ -22874,7 +22880,7 @@
     </row>
     <row r="202" ht="15.0" customHeight="1">
       <c r="A202" s="14" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B202" s="16">
         <v>1063.26</v>
@@ -22942,7 +22948,7 @@
     </row>
     <row r="203" ht="15.0" customHeight="1">
       <c r="A203" s="14" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B203" s="16">
         <v>850.61</v>
@@ -23008,7 +23014,7 @@
     </row>
     <row r="204" ht="15.0" customHeight="1">
       <c r="A204" s="14" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B204" s="16">
         <v>697.03</v>
@@ -23074,7 +23080,7 @@
     </row>
     <row r="205" ht="15.0" customHeight="1">
       <c r="A205" s="14" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B205" s="16">
         <v>590.7</v>
@@ -23140,7 +23146,7 @@
     </row>
     <row r="206" ht="15.0" customHeight="1">
       <c r="A206" s="14" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B206" s="16">
         <v>649.77</v>
@@ -23208,7 +23214,7 @@
     </row>
     <row r="207" ht="15.0" customHeight="1">
       <c r="A207" s="14" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B207" s="16">
         <v>5269.05</v>
@@ -23276,7 +23282,7 @@
     </row>
     <row r="208" ht="15.0" customHeight="1">
       <c r="A208" s="14" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B208" s="16">
         <v>527.32</v>
@@ -23350,7 +23356,7 @@
     </row>
     <row r="209" ht="15.0" customHeight="1">
       <c r="A209" s="14" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B209" s="16">
         <v>527.74</v>
@@ -23424,7 +23430,7 @@
     </row>
     <row r="210" ht="15.0" customHeight="1">
       <c r="A210" s="14" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B210" s="21">
         <v>0.41</v>
@@ -23498,7 +23504,7 @@
     </row>
     <row r="211" ht="15.0" customHeight="1">
       <c r="A211" s="14" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B211" s="21">
         <v>1.0</v>
@@ -23572,7 +23578,7 @@
     </row>
     <row r="212" ht="15.0" customHeight="1">
       <c r="A212" s="14" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B212" s="16">
         <v>527.74</v>
@@ -23646,7 +23652,7 @@
     </row>
     <row r="213" ht="15.0" customHeight="1">
       <c r="A213" s="14" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B213" s="16">
         <v>527.32</v>
@@ -23720,7 +23726,7 @@
     </row>
     <row r="214" ht="15.0" customHeight="1">
       <c r="A214" s="14" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B214" s="21">
         <v>0.41</v>
@@ -24599,7 +24605,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -24998,73 +25004,73 @@
         <v>45</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="X15" s="10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -25143,7 +25149,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -25319,7 +25325,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B21" s="16">
         <v>8695.01</v>
@@ -25517,7 +25523,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B24" s="16">
         <v>6951.33</v>
@@ -25653,7 +25659,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B26" s="16">
         <v>690.45</v>
@@ -25793,7 +25799,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B28" s="19">
         <v>-1111.74</v>
@@ -25857,7 +25863,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B29" s="16">
         <v>1462.82</v>
@@ -25905,7 +25911,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B30" s="16">
         <v>702.15</v>
@@ -25973,7 +25979,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B31" s="21">
         <v>11.7</v>
@@ -26013,7 +26019,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B32" s="16">
         <v>222.35</v>
@@ -26083,7 +26089,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B33" s="19">
         <v>-1474.52</v>
@@ -26153,7 +26159,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B34" s="21">
         <v>93.62</v>
@@ -26223,7 +26229,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -26277,7 +26283,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B36" s="19">
         <v>-280.86</v>
@@ -26321,7 +26327,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B37" s="19">
         <v>-1123.45</v>
@@ -26395,7 +26401,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B38" s="16">
         <v>4575.71</v>
@@ -26521,7 +26527,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B40" s="16">
         <v>4634.22</v>
@@ -26589,7 +26595,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B41" s="19">
         <v>-1497.93</v>
@@ -26657,7 +26663,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
@@ -26691,7 +26697,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B43" s="15"/>
       <c r="C43" s="15"/>
@@ -26729,7 +26735,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B44" s="20">
         <v>-11.7</v>
@@ -26773,7 +26779,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="17" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B45" s="18">
         <v>16442.11</v>
@@ -26847,7 +26853,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
@@ -26885,7 +26891,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B47" s="19">
         <v>-4259.74</v>
@@ -26959,7 +26965,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B48" s="19">
         <v>-748.96</v>
@@ -27003,7 +27009,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B49" s="15"/>
       <c r="C49" s="15"/>
@@ -27045,7 +27051,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B50" s="19">
         <v>-1451.12</v>
@@ -27081,7 +27087,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B51" s="16">
         <v>983.02</v>
@@ -27151,7 +27157,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B52" s="16">
         <v>234.05</v>
@@ -27193,7 +27199,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B53" s="15"/>
       <c r="C53" s="15"/>
@@ -27237,7 +27243,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B54" s="15"/>
       <c r="C54" s="15"/>
@@ -27291,7 +27297,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B55" s="15">
         <v>0.0</v>
@@ -27349,7 +27355,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B56" s="15">
         <v>0.0</v>
@@ -27401,7 +27407,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B57" s="15"/>
       <c r="C57" s="15"/>
@@ -27433,7 +27439,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B58" s="15">
         <v>0.0</v>
@@ -27501,7 +27507,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B59" s="16">
         <v>234.05</v>
@@ -27549,7 +27555,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B60" s="15">
         <v>0.0</v>
@@ -27619,7 +27625,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B61" s="15"/>
       <c r="C61" s="15"/>
@@ -27657,7 +27663,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B62" s="15"/>
       <c r="C62" s="15"/>
@@ -27689,7 +27695,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B63" s="15"/>
       <c r="C63" s="15"/>
@@ -27723,7 +27729,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B64" s="15"/>
       <c r="C64" s="15"/>
@@ -27769,7 +27775,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B65" s="15"/>
       <c r="C65" s="20">
@@ -27807,7 +27813,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="17" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B66" s="25">
         <v>-5008.7</v>
@@ -27881,7 +27887,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B67" s="16">
         <v>760.67</v>
@@ -27951,7 +27957,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B68" s="19">
         <v>-1731.98</v>
@@ -28021,7 +28027,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B69" s="19">
         <v>-1310.69</v>
@@ -28065,7 +28071,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B70" s="16">
         <v>374.48</v>
@@ -28135,7 +28141,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B71" s="16">
         <v>163.84</v>
@@ -28183,7 +28189,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B72" s="19">
         <v>-1872.41</v>
@@ -28213,7 +28219,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B73" s="19">
         <v>-9268.44</v>
@@ -28287,7 +28293,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B74" s="19">
         <v>-269.16</v>
@@ -28327,7 +28333,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B75" s="20">
         <v>-93.62</v>
@@ -28369,7 +28375,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B76" s="15"/>
       <c r="C76" s="15"/>
@@ -28403,7 +28409,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B77" s="20">
         <v>-11.7</v>
@@ -28469,7 +28475,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B78" s="15"/>
       <c r="C78" s="15"/>
@@ -28501,7 +28507,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B79" s="15"/>
       <c r="C79" s="15"/>
@@ -28547,7 +28553,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B80" s="15"/>
       <c r="C80" s="15"/>
@@ -28585,7 +28591,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B81" s="20">
         <v>-23.41</v>
@@ -28625,7 +28631,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="17" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B82" s="29">
         <v>-13282.42</v>
@@ -28699,7 +28705,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B83" s="15">
         <v>0.0</v>
@@ -28733,7 +28739,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="17" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B84" s="18">
         <v>0.0</v>
@@ -28767,7 +28773,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B85" s="15">
         <v>10538.09</v>
@@ -28841,7 +28847,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="14" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B86" s="19">
         <v>-222.35</v>
@@ -28915,7 +28921,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="14" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B87" s="19">
         <v>-1849.01</v>
@@ -28971,7 +28977,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="14" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B88" s="16">
         <v>8447.02</v>
@@ -29045,7 +29051,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="17" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B89" s="25">
         <v>-2071.36</v>
@@ -29119,7 +29125,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="14" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B90" s="15">
         <v>11433.41</v>
@@ -30084,7 +30090,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -30265,31 +30271,31 @@
         <v>40</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AB11" s="7" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AC11" s="7" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AD11" s="7" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AE11" s="7" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AF11" s="7" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AG11" s="7" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -30789,7 +30795,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -30898,36 +30904,36 @@
         <v>72</v>
       </c>
       <c r="Y19" s="13" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="Z19" s="13" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AA19" s="13" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AC19" s="13" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AD19" s="13" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AE19" s="13" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AF19" s="13" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AG19" s="13" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="30" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B20" s="31"/>
       <c r="C20" s="31"/>
@@ -30964,7 +30970,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="32" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B21" s="33">
         <v>193496.52</v>
@@ -31061,7 +31067,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="32" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B22" s="33">
         <v>225491.14</v>
@@ -31150,7 +31156,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="30" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B23" s="31"/>
       <c r="C23" s="31"/>
@@ -31187,7 +31193,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="32" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B24" s="33">
         <v>154557.55</v>
@@ -31284,7 +31290,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="32" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B25" s="33">
         <v>193607.5</v>
@@ -31373,7 +31379,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="30" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B26" s="31"/>
       <c r="C26" s="31"/>
@@ -31410,7 +31416,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="32" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B27" s="34">
         <v>292.87</v>
@@ -31507,7 +31513,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="32" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B28" s="34">
         <v>363.4</v>
@@ -31596,7 +31602,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="30" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B29" s="31"/>
       <c r="C29" s="31"/>
@@ -31633,7 +31639,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="32" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B30" s="36">
         <v>7.46</v>
@@ -31730,7 +31736,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="32" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B31" s="36">
         <v>2.06</v>
@@ -31819,7 +31825,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="30" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B32" s="31"/>
       <c r="C32" s="31"/>
@@ -31856,7 +31862,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="32" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B33" s="36">
         <v>6.05</v>
@@ -31945,7 +31951,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="32" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B34" s="36">
         <v>4.62</v>
@@ -32010,7 +32016,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="32" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B35" s="36">
         <v>6.05</v>
@@ -32107,7 +32113,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="32" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B36" s="36">
         <v>4.62</v>
@@ -32196,7 +32202,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="30" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B37" s="31"/>
       <c r="C37" s="31"/>
@@ -32233,7 +32239,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="32" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B38" s="35">
         <v>1.31</v>
@@ -32330,7 +32336,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="32" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B39" s="35">
         <v>1.47</v>
@@ -32419,7 +32425,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="30" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B40" s="31"/>
       <c r="C40" s="31"/>
@@ -32456,7 +32462,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="32" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B41" s="35">
         <v>1.42</v>
@@ -32553,7 +32559,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="32" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B42" s="35">
         <v>1.59</v>
@@ -32642,7 +32648,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="30" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B43" s="31"/>
       <c r="C43" s="31"/>
@@ -32679,7 +32685,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="32" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B44" s="35">
         <v>1.36</v>
@@ -32776,7 +32782,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="32" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B45" s="35">
         <v>1.58</v>
@@ -32865,7 +32871,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="30" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B46" s="31"/>
       <c r="C46" s="31"/>
@@ -32902,7 +32908,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="32" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B47" s="35">
         <v>13.41</v>
@@ -32995,7 +33001,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="32" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B48" s="35">
         <v>48.51</v>
@@ -33084,7 +33090,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="30" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B49" s="31"/>
       <c r="C49" s="31"/>
@@ -33121,7 +33127,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="32" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B50" s="35">
         <v>12.68</v>
@@ -33216,7 +33222,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="32" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B51" s="35">
         <v>12.06</v>
@@ -33305,7 +33311,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="30" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B52" s="31"/>
       <c r="C52" s="31"/>
@@ -33342,7 +33348,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="32" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B53" s="35">
         <v>27.3</v>
@@ -33435,7 +33441,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="32" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B54" s="35">
         <v>19.91</v>
@@ -33522,7 +33528,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="30" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B55" s="31"/>
       <c r="C55" s="31"/>
@@ -33559,7 +33565,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="32" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B56" s="35">
         <v>27.47</v>
@@ -33654,7 +33660,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="32" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B57" s="35">
         <v>1.47</v>
@@ -33743,7 +33749,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="30" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B58" s="31"/>
       <c r="C58" s="31"/>
@@ -33780,7 +33786,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="32" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B59" s="35">
         <v>2.46</v>
@@ -33873,7 +33879,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="32" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B60" s="38">
         <v>-6.96</v>
@@ -33954,7 +33960,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="30" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B61" s="31"/>
       <c r="C61" s="31"/>
@@ -33991,7 +33997,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="32" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B62" s="35">
         <v>1.7</v>
@@ -34088,7 +34094,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="32" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B63" s="35">
         <v>1.84</v>
@@ -34177,7 +34183,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="30" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B64" s="31"/>
       <c r="C64" s="31"/>
@@ -34214,7 +34220,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="32" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B65" s="35">
         <v>13.57</v>
@@ -34311,7 +34317,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="32" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B66" s="35">
         <v>10.68</v>
@@ -34400,7 +34406,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="30" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B67" s="31"/>
       <c r="C67" s="31"/>
@@ -34437,7 +34443,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="32" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B68" s="35">
         <v>11.66</v>
@@ -34534,7 +34540,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="32" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B69" s="35">
         <v>14.07</v>
@@ -34623,7 +34629,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="30" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B70" s="31"/>
       <c r="C70" s="31"/>
@@ -34660,7 +34666,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="32" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B71" s="35">
         <v>16.76</v>
@@ -34753,7 +34759,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="32" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B72" s="35">
         <v>56.74</v>
